--- a/Outputs/Scenarios/PtX_demand_BG_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_BG_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.0009103253911235636</v>
       </c>
       <c r="K16" t="n">
-        <v>0.001516180492622159</v>
+        <v>0.001913808322212921</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.002526967487703597</v>
+        <v>0.002198088657235992</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>1.311624796363922e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001010786995081439</v>
+        <v>0.0009420379959582826</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.001347625912720067</v>
       </c>
       <c r="K30" t="n">
-        <v>0.008093295968494871</v>
+        <v>0.01021581352220822</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.01348882661415812</v>
+        <v>0.01173328779427562</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>7.092767961684565e-05</v>
       </c>
       <c r="K42" t="n">
-        <v>0.005395530645663249</v>
+        <v>0.005028551911832407</v>
       </c>
     </row>
     <row r="43">
